--- a/out/LSTM-Mamba1_repeat_3_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004335500349259237</v>
+        <v>-5.113152705365792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5580126668720173</v>
+        <v>0.06581025827228758</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.117081362129436</v>
+        <v>0.1317450612097988</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1288680609038925</v>
+        <v>-0.01519829364927153</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4287110559331989</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4287110559331989</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4286948689304841</v>
+        <v>0.05049346794002224</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.04972997309167111</v>
+        <v>0.2069603280649097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5282538391135356</v>
+        <v>0.4648262304554276</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009515207914236974</v>
+        <v>0.03959946472118359</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4974818350530509</v>
+        <v>0.3367629381030302</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01666678906592552</v>
+        <v>0.0693624355333953</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5213051808992764</v>
+        <v>0.4359076316691118</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.009125690442939814</v>
+        <v>0.0379851555764479</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.522877098230951</v>
+        <v>0.4424561980214322</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00376616100603499</v>
+        <v>0.01568861925315071</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5212759921360793</v>
+        <v>0.4358079836439788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.004693806849316354</v>
+        <v>0.0195461828627473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5268975572939398</v>
+        <v>0.4592153450370701</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.002823682370270864</v>
+        <v>0.01176817925537965</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5278497474935143</v>
+        <v>0.463193604961955</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.002145539255363825</v>
+        <v>0.008945698889074837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5293167927408289</v>
+        <v>0.4693134159177437</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0009469859472717061</v>
+        <v>0.003953926535315225</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5290619105991973</v>
+        <v>0.4682690490630101</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0007491413321628715</v>
+        <v>0.003137675919314173</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5296154569116532</v>
+        <v>0.470587744349756</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0003702220394957571</v>
+        <v>0.001553422204039044</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5296037601295069</v>
+        <v>0.4705549303812415</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0002131900559222156</v>
+        <v>0.0008997614318907874</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5296597200183675</v>
+        <v>0.470803118930717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.000102640427588293</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5296545859987689</v>
+        <v>0.470797553875112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>4.961831508525235e-05</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5296482033909851</v>
+        <v>0.4707868779063155</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>2.503887500112463e-05</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5296519738156649</v>
+        <v>0.4708178743160781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>6.159850569859539e-06</v>
+        <v>3.740743216546624e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5296358896624019</v>
+        <v>0.4707696475226011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-5.08417705457914e-07</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5296309532003876</v>
+        <v>0.470764896024337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-2.553803869891494e-06</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5296265520717826</v>
+        <v>0.4707618871525233</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.629819553036738e-06</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5296213968832097</v>
+        <v>0.4707565006683657</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5296219365511099</v>
+        <v>0.4707531160499149</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5296216044477867</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5296219849828444</v>
+        <v>0.4707478291546989</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5296222133038792</v>
+        <v>0.4707480574757336</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5296223032485291</v>
+        <v>0.4707481474203835</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5296214453149443</v>
+        <v>0.4707472894867987</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5296216736359789</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5296208779717673</v>
+        <v>0.4707467221436217</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5296209402411403</v>
+        <v>0.4707467844129947</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5296209679164172</v>
+        <v>0.4707468120882716</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5296211201304405</v>
+        <v>0.4707469643022949</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5296207741894787</v>
+        <v>0.4707466183613331</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5296208502964903</v>
+        <v>0.4707466944683448</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.529621016348152</v>
+        <v>0.4707468605200064</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.529621376126752</v>
+        <v>0.4707472202986064</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5296213968832097</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5296215006654982</v>
+        <v>0.4707473448373526</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5296217289865329</v>
+        <v>0.4707475731583873</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5296216044477867</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5296216321230636</v>
+        <v>0.470747476294918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5296216874736175</v>
+        <v>0.470747531645472</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5296219503887482</v>
+        <v>0.4707477945606026</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5296218673629174</v>
+        <v>0.4707477115347719</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5296216597983406</v>
+        <v>0.470747503970195</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5296216736359789</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5296218120123637</v>
+        <v>0.4707476561842181</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.529621528340775</v>
+        <v>0.4707473725126295</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5296213553702943</v>
+        <v>0.4707471995421487</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5296212515880058</v>
+        <v>0.4707470957598602</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5296213968832097</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.529621639041883</v>
+        <v>0.4707474832137374</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5296214660714019</v>
+        <v>0.4707473102432564</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.529621168562175</v>
+        <v>0.4707470127340295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5296211547245364</v>
+        <v>0.4707469988963909</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5296207880271172</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5296207880271172</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5296207257577442</v>
+        <v>0.4707465699295986</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5296206219754557</v>
+        <v>0.4707464661473101</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.529620449004975</v>
+        <v>0.4707462931768294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5296204974367095</v>
+        <v>0.4707463416085639</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5296201376581094</v>
+        <v>0.4707459818299639</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.529620096145194</v>
+        <v>0.4707459403170485</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5296201514957477</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5296202068463016</v>
+        <v>0.4707460510181561</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5296202483592171</v>
+        <v>0.4707460925310715</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.529619978525267</v>
+        <v>0.4707458226971214</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5296200338758209</v>
+        <v>0.4707458780476754</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5296201791710248</v>
+        <v>0.4707460233428792</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5296201445769286</v>
+        <v>0.470745988748783</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.52962013073929</v>
+        <v>0.4707459749111444</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5296202206839402</v>
+        <v>0.4707460648557947</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5296205389496249</v>
+        <v>0.4707463831214793</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5296203590603247</v>
+        <v>0.4707462032321791</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5296204005732401</v>
+        <v>0.4707462447450946</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5296202137651208</v>
+        <v>0.4707460579369753</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5296202829533133</v>
+        <v>0.4707461271251678</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5296200823075555</v>
+        <v>0.4707459264794099</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5296201238204709</v>
+        <v>0.4707459679923253</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5296201514957477</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.305762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.305762781659078</v>
+        <v>0.979279226522314</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004335500349259237</v>
+        <v>-0.0003234725534667959</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5580126668720173</v>
+        <v>0.4163341631488183</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.117081362129436</v>
+        <v>0.8334566526871295</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1288680609038925</v>
+        <v>-0.09614876815877423</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4287110559331989</v>
+        <v>0.3198619224365773</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4287110559331989</v>
+        <v>0.3198619224365773</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4286948689304841</v>
+        <v>0.3197917548490786</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.04972997309167111</v>
+        <v>0.2155700038928903</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5282538391135356</v>
+        <v>0.7513610128973401</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009515207914236974</v>
+        <v>0.04124689127676406</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4974818350530509</v>
+        <v>0.6179702093250805</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01666678906592552</v>
+        <v>0.07224784184761734</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5213051808992764</v>
+        <v>0.7212392206524587</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.009125690442939814</v>
+        <v>0.03956530907577049</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.522877098230951</v>
+        <v>0.728060200643301</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00376616100603499</v>
+        <v>0.01634124566060044</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5212759921360793</v>
+        <v>0.7211354290879913</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.004693806849316354</v>
+        <v>0.02035929936180479</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5268975572939398</v>
+        <v>0.7455165066121682</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.002823682370270864</v>
+        <v>0.01225853146242326</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5278497474935143</v>
+        <v>0.7496604600704238</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.002145539255363825</v>
+        <v>0.009317596655040008</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5293167927408289</v>
+        <v>0.7560347287545227</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0009469859472717061</v>
+        <v>0.004119212910133685</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5290619105991973</v>
+        <v>0.7549471842511283</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0007491413321628715</v>
+        <v>0.003266308721790115</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5296154569116532</v>
+        <v>0.7573619247017642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0003702220394957571</v>
+        <v>0.001618460690884975</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5296037601295069</v>
+        <v>0.7573279499576776</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0002131900559222156</v>
+        <v>0.0009375810415839713</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5296597200183675</v>
+        <v>0.757586704887889</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.000102640427588293</v>
+        <v>0.0004662905207919857</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5296545859987689</v>
+        <v>0.7575811180993761</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>4.961831508525235e-05</v>
+        <v>0.0002278465011529179</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5296482033909851</v>
+        <v>0.7575701892299911</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>2.503887500112463e-05</v>
+        <v>0.0001318437638940122</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5296519738156649</v>
+        <v>0.7576030316094852</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>6.159850569859539e-06</v>
+        <v>3.963940227943816e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5296358896624019</v>
+        <v>0.7575525879853554</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-5.08417705457914e-07</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5296309532003876</v>
+        <v>0.7575478503247299</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-2.553803869891494e-06</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5296265520717826</v>
+        <v>0.757545042098674</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.629819553036738e-06</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5296213968832097</v>
+        <v>0.757539576532955</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5296219365511099</v>
+        <v>0.7575361919145042</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5296216044477867</v>
+        <v>0.7575305244842304</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5296219849828444</v>
+        <v>0.7575309050192882</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5296222133038792</v>
+        <v>0.7575311333403228</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5296223032485291</v>
+        <v>0.7575312232849728</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5296214453149443</v>
+        <v>0.757530365351388</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5296216736359789</v>
+        <v>0.7575305936724227</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5296208779717673</v>
+        <v>0.757529798008211</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5296209402411403</v>
+        <v>0.7575298602775841</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5296209679164172</v>
+        <v>0.7575298879528609</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5296211201304405</v>
+        <v>0.7575300401668842</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5296207741894787</v>
+        <v>0.7575296942259224</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5296208502964903</v>
+        <v>0.7575297703329341</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.529621016348152</v>
+        <v>0.7575299363845956</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.529621376126752</v>
+        <v>0.7575302961631958</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5296213968832097</v>
+        <v>0.7575303169196534</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5296215006654982</v>
+        <v>0.757530420701942</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5296217289865329</v>
+        <v>0.7575306490229766</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5296216044477867</v>
+        <v>0.7575305244842304</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5296216321230636</v>
+        <v>0.7575305521595073</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5296216874736175</v>
+        <v>0.7575306075100612</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5296219503887482</v>
+        <v>0.757530870425192</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5296218673629174</v>
+        <v>0.7575307873993612</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5296216597983406</v>
+        <v>0.7575305798347843</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5296216736359789</v>
+        <v>0.7575305936724227</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5296218120123637</v>
+        <v>0.7575307320488074</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.529621528340775</v>
+        <v>0.7575304483772188</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5296213553702943</v>
+        <v>0.757530275406738</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5296212515880058</v>
+        <v>0.7575301716244496</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5296213968832097</v>
+        <v>0.7575303169196534</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.529621639041883</v>
+        <v>0.7575305590783267</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5296214660714019</v>
+        <v>0.7575303861078457</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.529621168562175</v>
+        <v>0.7575300885986187</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5296211547245364</v>
+        <v>0.7575300747609802</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5296207880271172</v>
+        <v>0.757529708063561</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5296207880271172</v>
+        <v>0.757529708063561</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5296207257577442</v>
+        <v>0.7575296457941879</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5296206219754557</v>
+        <v>0.7575295420118994</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.529620449004975</v>
+        <v>0.7575293690414187</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5296204974367095</v>
+        <v>0.7575294174731532</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5296201376581094</v>
+        <v>0.7575290576945531</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.529620096145194</v>
+        <v>0.7575290161816378</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5296201514957477</v>
+        <v>0.7575290715321915</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5296202068463016</v>
+        <v>0.7575291268827454</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5296202483592171</v>
+        <v>0.7575291683956609</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.529619978525267</v>
+        <v>0.7575288985617107</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5296200338758209</v>
+        <v>0.7575289539122647</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5296201791710248</v>
+        <v>0.7575290992074686</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5296201445769286</v>
+        <v>0.7575290646133723</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.52962013073929</v>
+        <v>0.7575290507757337</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5296202206839402</v>
+        <v>0.7575291407203839</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5296205389496249</v>
+        <v>0.7575294589860686</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5296203590603247</v>
+        <v>0.7575292790967685</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5296204005732401</v>
+        <v>0.7575293206096839</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5296202137651208</v>
+        <v>0.7575291338015646</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5296202829533133</v>
+        <v>0.757529202989757</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5296200823075555</v>
+        <v>0.7575290023439992</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5296201238204709</v>
+        <v>0.7575290438569147</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5296201514957477</v>
+        <v>0.7575290715321915</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02265223115682602</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01296704635024071</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007215648889541626</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.003751181066036224</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.002038184553384781</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0009773410856723785</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0006034411489963531</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0001196153461933136</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.2117496884784028</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0001851879060268402</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.179279226522314</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0001030527055263519</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.179279226522314</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-5.614385008811951e-05</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0001574940979480743</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>9.678676724433899e-05</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.179279226522314</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0001429878175258636</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.946808764566225</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>9.714439511299133e-05</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.946808764566225</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>5.700066685676575e-05</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.946808764566225</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0002264343202114105</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.946808764566225</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0004826709628105164</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.946808764566225</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0008159615099430084</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0007201395928859711</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.946808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0004506520926952362</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.946808764566225</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0001628585159778595</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.946808764566225</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>4.924461245536804e-05</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0003857165575027466</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0003566257655620575</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0007209032773971558</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.746808764566225</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001599162817001343</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.746808764566225</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.00136512890458107</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.746808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0006293915212154388</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.746808764566225</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0001444593071937561</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.979279226522314</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0003002583980560303</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0006036646664142609</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0005609020590782166</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0001043155789375305</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0001666508615016937</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>5.074962973594666e-05</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.946808764566225</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>7.118284702301025e-05</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0001720897853374481</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0002688392996788025</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0001431405544281006</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.0002456121146678925</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9792792265223138</v>
+        <v>0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0006816387176513672</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.946808764566225</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.001409959048032761</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.946808764566225</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003234725534667959</v>
+        <v>-0.0001665776765915798</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4163341631488183</v>
+        <v>0.2143982350876445</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.001175139099359512</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.179279226522314</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8334566526871295</v>
+        <v>0.4292026366520683</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09614876815877423</v>
+        <v>-0.04951346215049699</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.00048108771443367</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3198619224365773</v>
+        <v>0.1647181952605559</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001380197703838348</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3198619224365773</v>
+        <v>0.1647181952605559</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001701734960079193</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3197917548490786</v>
+        <v>0.1646998776746264</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2155700038928903</v>
+        <v>0.0562755855073121</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.002144813537597656</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7513610128973401</v>
+        <v>0.2773631065331716</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.04124689127676406</v>
+        <v>0.0107676991930179</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001817811280488968</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6179702093250805</v>
+        <v>0.2425407962081714</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.07224784184761734</v>
+        <v>0.01886042878792605</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.001724876463413239</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7212392206524587</v>
+        <v>0.2694996683138143</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.03956530907577049</v>
+        <v>0.01032744833197872</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.00179324671626091</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.728060200643301</v>
+        <v>0.2712791299672541</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01634124566060044</v>
+        <v>0.004262708362055678</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.002223782241344452</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7211354290879913</v>
+        <v>0.2694679591389922</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02035929936180479</v>
+        <v>0.005311941807568455</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.001494541764259338</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7455165066121682</v>
+        <v>0.2758297072263686</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01225853146242326</v>
+        <v>0.003195877418990714</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.001933377236127853</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7496604600704238</v>
+        <v>0.276907817104077</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.009317596655040008</v>
+        <v>0.00242940325064159</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.001416638493537903</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7560347287545227</v>
+        <v>0.2785684703497791</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004119212910133685</v>
+        <v>0.001070950728385551</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003016311675310135</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7549471842511283</v>
+        <v>0.2782808417336421</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003266308721790115</v>
+        <v>0.0008500298046930216</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.003950905054807663</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7573619247017642</v>
+        <v>0.2789080509649478</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001618460690884975</v>
+        <v>0.0004177501644985529</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.002192988991737366</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7573279499576776</v>
+        <v>0.2788954851672719</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0009375810415839713</v>
+        <v>0.000242282063378511</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.00178830698132515</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.757586704887889</v>
+        <v>0.2789595730413136</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0004662905207919857</v>
+        <v>0.0001171864313164407</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003809470683336258</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7575811180993761</v>
+        <v>0.2789544209109585</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002278465011529179</v>
+        <v>5.536761141001575e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.005370855331420898</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7575701892299911</v>
+        <v>0.2789478581714169</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001318437638940122</v>
+        <v>3.17141805569301e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.006442546844482422</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7576030316094852</v>
+        <v>0.2789530110049399</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>3.963940227943816e-05</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.007932769134640694</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7575525879853554</v>
+        <v>0.2789358198405996</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.745791147271043e-05</v>
+        <v>1.73737344181313e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.008469540625810623</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7575478503247299</v>
+        <v>0.2789308943911204</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.230980650542531e-06</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.008593494072556496</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.757545042098674</v>
+        <v>0.2789264932625154</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.007825523614883423</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.757539576532955</v>
+        <v>0.2789213380739426</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.007062334567308426</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7575361919145042</v>
+        <v>0.2789218777418427</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.006726581603288651</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7575305244842304</v>
+        <v>0.2789215456385196</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006162106990814209</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7575309050192882</v>
+        <v>0.2789219261735773</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.006558991968631744</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7575311333403228</v>
+        <v>0.278922154494612</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.007086869329214096</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7575312232849728</v>
+        <v>0.2789222444392619</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.007544547319412231</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.757530365351388</v>
+        <v>0.2789213865056771</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.007597275078296661</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7575305936724227</v>
+        <v>0.2789216148267119</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.007555700838565826</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.757529798008211</v>
+        <v>0.2789208191625001</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.007657252252101898</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7575298602775841</v>
+        <v>0.2789208814318732</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.007248826324939728</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7575298879528609</v>
+        <v>0.2789209091071501</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.00646548718214035</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7575300401668842</v>
+        <v>0.2789210613211733</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.006396640092134476</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7575296942259224</v>
+        <v>0.2789207153802116</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.006045270711183548</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7575297703329341</v>
+        <v>0.2789207914872233</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.005965162068605423</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7575299363845956</v>
+        <v>0.2789209575388849</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005034368485212326</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7575302961631958</v>
+        <v>0.2789213173174849</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.004450008273124695</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7575303169196534</v>
+        <v>0.2789213380739426</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.004087887704372406</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.757530420701942</v>
+        <v>0.2789214418562311</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.004692170768976212</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7575306490229766</v>
+        <v>0.2789216701772658</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.005457870662212372</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7575305244842304</v>
+        <v>0.2789215456385196</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.005993533879518509</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7575305521595073</v>
+        <v>0.2789215733137964</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.005548875778913498</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7575306075100612</v>
+        <v>0.2789216286643504</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.00571674108505249</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.757530870425192</v>
+        <v>0.2789218915794811</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.005844727158546448</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7575307873993612</v>
+        <v>0.2789218085536503</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.005987875163555145</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7575305798347843</v>
+        <v>0.2789216009890735</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.006001561880111694</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7575305936724227</v>
+        <v>0.2789216148267119</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.005977202206850052</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7575307320488074</v>
+        <v>0.2789217532030966</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.006143815815448761</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7575304483772188</v>
+        <v>0.2789214695315079</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.006242018193006516</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.757530275406738</v>
+        <v>0.2789212965610272</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005728553980588913</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7575301716244496</v>
+        <v>0.2789211927787387</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.005372393876314163</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7575303169196534</v>
+        <v>0.2789213380739426</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.005226351320743561</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7575305590783267</v>
+        <v>0.2789215802326158</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.00542180985212326</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7575303861078457</v>
+        <v>0.2789214072621348</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005607802420854568</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7575300885986187</v>
+        <v>0.2789211097529079</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005712978541851044</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7575300747609802</v>
+        <v>0.2789210959152693</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005726858973503113</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.757529708063561</v>
+        <v>0.2789207292178502</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.005300909280776978</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.757529708063561</v>
+        <v>0.2789207292178502</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.004976771771907806</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7575296457941879</v>
+        <v>0.2789206669484771</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.005117226392030716</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7575295420118994</v>
+        <v>0.2789205631661885</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.005112756043672562</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7575293690414187</v>
+        <v>0.2789203901957078</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.005002763122320175</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7575294174731532</v>
+        <v>0.2789204386274424</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.005014237016439438</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7575290576945531</v>
+        <v>0.2789200788488423</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004809904843568802</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7575290161816378</v>
+        <v>0.2789200373359269</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004304703325033188</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7575290715321915</v>
+        <v>0.2789200926864806</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004101131111383438</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7575291268827454</v>
+        <v>0.2789201480370346</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003939542919397354</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7575291683956609</v>
+        <v>0.27892018954995</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003915689885616302</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7575288985617107</v>
+        <v>0.2789199197159998</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003646846860647202</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7575289539122647</v>
+        <v>0.2789199750665538</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003443099558353424</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7575290992074686</v>
+        <v>0.2789201203617577</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003255125135183334</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7575290646133723</v>
+        <v>0.2789200857676615</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00325484573841095</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7575290507757337</v>
+        <v>0.2789200719300229</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002704206854104996</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7575291407203839</v>
+        <v>0.2789201618746731</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.00179552286863327</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7575294589860686</v>
+        <v>0.2789204801403578</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002517305314540863</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7575292790967685</v>
+        <v>0.2789203002510576</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003361273556947708</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7575293206096839</v>
+        <v>0.278920341763973</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003894742578268051</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7575291338015646</v>
+        <v>0.2789201549558537</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.004305474460124969</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.757529202989757</v>
+        <v>0.2789202241440462</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.004348892718553543</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7575290023439992</v>
+        <v>0.2789200234982884</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004274927079677582</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7575290438569147</v>
+        <v>0.2789200650112038</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003915488719940186</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7575290715321915</v>
+        <v>0.2789200926864806</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.02265223115682602</v>
+        <v>-0.02265222743153572</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.01296704635024071</v>
+        <v>-0.01296709291636944</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.007215648889541626</v>
+        <v>-0.00721561536192894</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.002038184553384781</v>
+        <v>-0.002038143575191498</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.16</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0009773410856723785</v>
+        <v>-0.0009773336350917816</v>
       </c>
       <c r="JB7" t="n">
         <v>0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0006034411489963531</v>
+        <v>-0.000603456050157547</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0001196153461933136</v>
+        <v>-0.0001196302473545074</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.0001851879060268402</v>
+        <v>0.0001852624118328094</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.0001030527055263519</v>
+        <v>0.0001030266284942627</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-5.614385008811951e-05</v>
+        <v>-5.61252236366272e-05</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0001574940979480743</v>
+        <v>-0.0001575015485286713</v>
       </c>
       <c r="JB13" t="n">
         <v>0.8599999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>9.678676724433899e-05</v>
+        <v>9.670481085777283e-05</v>
       </c>
       <c r="JB14" t="n">
         <v>0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0001429878175258636</v>
+        <v>0.0001429766416549683</v>
       </c>
       <c r="JB15" t="n">
         <v>0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>9.714439511299133e-05</v>
+        <v>9.70400869846344e-05</v>
       </c>
       <c r="JB16" t="n">
         <v>0.1199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>5.700066685676575e-05</v>
+        <v>5.697458982467651e-05</v>
       </c>
       <c r="JB17" t="n">
         <v>0.1199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0002264343202114105</v>
+        <v>0.0002263858914375305</v>
       </c>
       <c r="JB18" t="n">
         <v>0.2599999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0004826709628105164</v>
+        <v>0.0004825741052627563</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.0008159615099430084</v>
+        <v>0.0008158721029758453</v>
       </c>
       <c r="JB20" t="n">
         <v>0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0007201395928859711</v>
+        <v>0.0007201358675956726</v>
       </c>
       <c r="JB21" t="n">
         <v>0.8599999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.0004506520926952362</v>
+        <v>0.0004506409168243408</v>
       </c>
       <c r="JB22" t="n">
         <v>0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.0001628585159778595</v>
+        <v>0.0001628920435905457</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.02000000000000007</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>4.924461245536804e-05</v>
+        <v>4.925951361656189e-05</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0003857165575027466</v>
+        <v>0.0003857351839542389</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0003566257655620575</v>
+        <v>0.0003566592931747437</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.02000000000000007</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0007209032773971558</v>
+        <v>0.000720929354429245</v>
       </c>
       <c r="JB27" t="n">
         <v>0.1199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001599162817001343</v>
+        <v>0.001599129289388657</v>
       </c>
       <c r="JB28" t="n">
         <v>0.2599999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.00136512890458107</v>
+        <v>0.001365087926387787</v>
       </c>
       <c r="JB29" t="n">
         <v>0.8599999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.0006293915212154388</v>
+        <v>0.0006293691694736481</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.0001444593071937561</v>
+        <v>0.0001445040106773376</v>
       </c>
       <c r="JB31" t="n">
         <v>0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0003002583980560303</v>
+        <v>-0.0003003068268299103</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0006036646664142609</v>
+        <v>-0.0006036907434463501</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0005609020590782166</v>
+        <v>-0.0005609095096588135</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.0001043155789375305</v>
+        <v>0.0001042522490024567</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.0001666508615016937</v>
+        <v>0.000166621059179306</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>5.074962973594666e-05</v>
+        <v>5.072355270385742e-05</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>7.118284702301025e-05</v>
+        <v>7.116422057151794e-05</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0001720897853374481</v>
+        <v>-0.0001721158623695374</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0002688392996788025</v>
+        <v>-0.0002689100801944733</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0001431405544281006</v>
+        <v>-0.0001431927084922791</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.5799999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.0002456121146678925</v>
+        <v>0.0002455748617649078</v>
       </c>
       <c r="JB42" t="n">
         <v>0.3</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.0006816387176513672</v>
+        <v>0.0006816089153289795</v>
       </c>
       <c r="JB43" t="n">
         <v>0.5799999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.001409959048032761</v>
+        <v>0.001409951597452164</v>
       </c>
       <c r="JB44" t="n">
         <v>0.5799999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.001175139099359512</v>
+        <v>0.001175183802843094</v>
       </c>
       <c r="JB45" t="n">
         <v>0.4399999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.00048108771443367</v>
+        <v>-0.0004810579121112823</v>
       </c>
       <c r="JB46" t="n">
         <v>0.16</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001380197703838348</v>
+        <v>-0.00138019397854805</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.1199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001701734960079193</v>
+        <v>-0.001701753586530685</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.002144813537597656</v>
+        <v>-0.002144847065210342</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.001817811280488968</v>
+        <v>-0.001817826181650162</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.001724876463413239</v>
+        <v>-0.001724880188703537</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.00179324671626091</v>
+        <v>-0.001793280243873596</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.002223782241344452</v>
+        <v>-0.002223793417215347</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.001494541764259338</v>
+        <v>-0.001494549214839935</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.001933377236127853</v>
+        <v>-0.001933235675096512</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.001416638493537903</v>
+        <v>-0.001416601240634918</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.003016311675310135</v>
+        <v>-0.003016281872987747</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.003950905054807663</v>
+        <v>-0.003950819373130798</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.002192988991737366</v>
+        <v>-0.00219285860657692</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.00178830698132515</v>
+        <v>-0.001788254827260971</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.003809470683336258</v>
+        <v>-0.003809418529272079</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.005370855331420898</v>
+        <v>-0.005370888859033585</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.006442546844482422</v>
+        <v>-0.006442710757255554</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.007932769134640694</v>
+        <v>-0.007932793349027634</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.008469540625810623</v>
+        <v>-0.008469568565487862</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.008593494072556496</v>
+        <v>-0.008593576028943062</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.007825523614883423</v>
+        <v>-0.007825504988431931</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.007062334567308426</v>
+        <v>-0.007062248885631561</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.006726581603288651</v>
+        <v>-0.006726372987031937</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.006162106990814209</v>
+        <v>-0.006162170320749283</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.006558991968631744</v>
+        <v>-0.006558969616889954</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.007086869329214096</v>
+        <v>-0.007086955010890961</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.007544547319412231</v>
+        <v>-0.00754450261592865</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.007597275078296661</v>
+        <v>-0.007597167044878006</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.007555700838565826</v>
+        <v>-0.007555600255727768</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.007657252252101898</v>
+        <v>-0.007657140493392944</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.007248826324939728</v>
+        <v>-0.007248595356941223</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.00646548718214035</v>
+        <v>-0.00646524503827095</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.006396640092134476</v>
+        <v>-0.006396587938070297</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.006045270711183548</v>
+        <v>-0.006045185029506683</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.1199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.005965162068605423</v>
+        <v>-0.005965165793895721</v>
       </c>
       <c r="JB81" t="n">
         <v>0.16</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.005034368485212326</v>
+        <v>-0.005034361034631729</v>
       </c>
       <c r="JB82" t="n">
         <v>0.4399999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.004450008273124695</v>
+        <v>-0.004449989646673203</v>
       </c>
       <c r="JB83" t="n">
         <v>0.7199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.004087887704372406</v>
+        <v>-0.004087831825017929</v>
       </c>
       <c r="JB84" t="n">
         <v>0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.004692170768976212</v>
+        <v>-0.004692114889621735</v>
       </c>
       <c r="JB85" t="n">
         <v>0.8599999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.005457870662212372</v>
+        <v>-0.00545777752995491</v>
       </c>
       <c r="JB86" t="n">
         <v>0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.005993533879518509</v>
+        <v>-0.005993187427520752</v>
       </c>
       <c r="JB87" t="n">
         <v>0.5799999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.005548875778913498</v>
+        <v>-0.005548637360334396</v>
       </c>
       <c r="JB88" t="n">
         <v>0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.00571674108505249</v>
+        <v>-0.005716700106859207</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.005844727158546448</v>
+        <v>-0.005844775587320328</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.005987875163555145</v>
+        <v>-0.005987830460071564</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.006001561880111694</v>
+        <v>-0.00600149855017662</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.005977202206850052</v>
+        <v>-0.005977082997560501</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.006143815815448761</v>
+        <v>-0.006143864244222641</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.006242018193006516</v>
+        <v>-0.006241951137781143</v>
       </c>
       <c r="JB95" t="n">
         <v>0.5799999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.005728553980588913</v>
+        <v>-0.005728486925363541</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.005372393876314163</v>
+        <v>-0.005372330546379089</v>
       </c>
       <c r="JB97" t="n">
         <v>0.8599999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.005226351320743561</v>
+        <v>-0.005226243287324905</v>
       </c>
       <c r="JB98" t="n">
         <v>0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.00542180985212326</v>
+        <v>-0.00542178750038147</v>
       </c>
       <c r="JB99" t="n">
         <v>0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.005607802420854568</v>
+        <v>-0.005607768893241882</v>
       </c>
       <c r="JB100" t="n">
         <v>0.8599999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.005712978541851044</v>
+        <v>-0.005712941288948059</v>
       </c>
       <c r="JB101" t="n">
         <v>0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.005726858973503113</v>
+        <v>-0.005726803094148636</v>
       </c>
       <c r="JB102" t="n">
         <v>0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.005300909280776978</v>
+        <v>-0.005300827324390411</v>
       </c>
       <c r="JB103" t="n">
         <v>0.1199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.004976771771907806</v>
+        <v>-0.004976559430360794</v>
       </c>
       <c r="JB104" t="n">
         <v>0.1199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.005117226392030716</v>
+        <v>-0.005117069929838181</v>
       </c>
       <c r="JB105" t="n">
         <v>0.2599999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.005112756043672562</v>
+        <v>-0.00511256605386734</v>
       </c>
       <c r="JB106" t="n">
         <v>0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.005002763122320175</v>
+        <v>-0.005002733319997787</v>
       </c>
       <c r="JB107" t="n">
         <v>0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.005014237016439438</v>
+        <v>-0.005014240741729736</v>
       </c>
       <c r="JB108" t="n">
         <v>0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.004809904843568802</v>
+        <v>-0.004809916019439697</v>
       </c>
       <c r="JB109" t="n">
         <v>0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.004304703325033188</v>
+        <v>-0.004304762929677963</v>
       </c>
       <c r="JB110" t="n">
         <v>0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.004101131111383438</v>
+        <v>-0.004101093858480453</v>
       </c>
       <c r="JB111" t="n">
         <v>0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003939542919397354</v>
+        <v>-0.003939434885978699</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003915689885616302</v>
+        <v>-0.003915559500455856</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.003646846860647202</v>
+        <v>-0.003646787256002426</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003443099558353424</v>
+        <v>-0.003442984074354172</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3999999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.003255125135183334</v>
+        <v>-0.003254998475313187</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3999999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.00325484573841095</v>
+        <v>-0.003254793584346771</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3999999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002704206854104996</v>
+        <v>-0.002704095095396042</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3999999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.00179552286863327</v>
+        <v>-0.001795414835214615</v>
       </c>
       <c r="JB119" t="n">
         <v>0.2599999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002517305314540863</v>
+        <v>-0.002517230808734894</v>
       </c>
       <c r="JB120" t="n">
         <v>0.1199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003361273556947708</v>
+        <v>-0.003361202776432037</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.02000000000000007</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003894742578268051</v>
+        <v>-0.00389472022652626</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.004305474460124969</v>
+        <v>-0.004305407404899597</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.004348892718553543</v>
+        <v>-0.004348885267972946</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.004274927079677582</v>
+        <v>-0.004274863749742508</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.3</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003915488719940186</v>
+        <v>-0.003915462642908096</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.3</v>
